--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,78 +482,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Idrott och hälsa 1 med didaktisk inriktning'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Endast engelsk variant</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Engelska Prerequisites finns (87 tecken) men svenska saknas</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Endast engelsk variant</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Engelska Prerequisites finns (142 tecken) men svenska saknas</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Idrott 2'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,110 +563,110 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 39 tecken vs en 84 tecken (×2.2)</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Diabetesvård I'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GNV3GU</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Endast engelsk variant</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Engelska Prerequisites finns (87 tecken) men svenska saknas</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Endast engelsk variant</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Engelska Prerequisites finns (142 tecken) men svenska saknas</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Osannolikt kort (23 tecken): '- Kandidatexamen 180 hp'</t>
+          <t>Längdskillnad sv 39 tecken vs en 84 tecken (×2.2)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>GNV3GU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,98 +676,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- Examen om minst 120 hp'</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GU</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VV3003</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 183 tecken vs en 35 tecken (×5.2)</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 104 tecken vs en 35 tecken (×3.0)</t>
+          <t>Osannolikt kort (23 tecken): '- Kandidatexamen 180 hp'</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>AVV2A6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (24 tecken): '- Examen om minst 120 hp'</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>VV3003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stor sv/en-längdskillnad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Längdskillnad sv 183 tecken vs en 35 tecken (×5.2)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>VV3004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Stor sv/en-längdskillnad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Längdskillnad sv 104 tecken vs en 35 tecken (×3.0)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>VV3009</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Längdskillnad sv 467 tecken vs en 219 tecken (×2.1)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -791,6 +872,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -482,12 +482,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Idrott och hälsa 1 med didaktisk inriktning'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,51 +509,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Idrott 2'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Diabetesvård I'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,24 +563,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Endast engelsk variant</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Diabetesvård I'</t>
+          <t>Engelska Prerequisites finns (87 tecken) men svenska saknas</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Engelska Prerequisites finns (87 tecken) men svenska saknas</t>
+          <t>Engelska Prerequisites finns (142 tecken) men svenska saknas</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,29 +617,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Endast engelsk variant</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engelska Prerequisites finns (142 tecken) men svenska saknas</t>
+          <t>Längdskillnad sv 39 tecken vs en 84 tecken (×2.2)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>VV3003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,206 +649,71 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 39 tecken vs en 84 tecken (×2.2)</t>
+          <t>Längdskillnad sv 183 tecken vs en 35 tecken (×5.2)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GNV3GU</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Längdskillnad sv 104 tecken vs en 35 tecken (×3.0)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>VV3009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Längdskillnad sv 467 tecken vs en 219 tecken (×2.1)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>ASA27E</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (23 tecken): '- Kandidatexamen 180 hp'</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>AVV2A6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (24 tecken): '- Examen om minst 120 hp'</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>VV3003</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 183 tecken vs en 35 tecken (×5.2)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>VV3004</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 104 tecken vs en 35 tecken (×3.0)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>VV3009</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 467 tecken vs en 219 tecken (×2.1)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -868,16 +733,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,170 +550,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>AMC28N</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Endast engelsk variant</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Engelska Prerequisites finns (87 tecken) men svenska saknas</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>AMC29F</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Endast engelsk variant</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Engelska Prerequisites finns (142 tecken) men svenska saknas</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>AMC2BG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 39 tecken vs en 84 tecken (×2.2)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>VV3003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 183 tecken vs en 35 tecken (×5.2)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>VV3004</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 104 tecken vs en 35 tecken (×3.0)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>VV3009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 467 tecken vs en 219 tecken (×2.1)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -721,18 +559,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,49 +509,400 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>AIH24T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AIH24T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GIH37R</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GIH37R</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GIH37S</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IH2001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>AMC265</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>MCA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Diabetesvård I'</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -559,6 +910,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,83 +536,83 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Diabetesvård I'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,73 +649,73 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Diabetesvård I'</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,147 +762,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>GSA2E5</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SD</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GSA2SE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FK</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -926,16 +791,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -553,34 +553,34 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Diabetesvård I'</t>
+          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -600,14 +600,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,14 +627,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -681,14 +681,14 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,39 +735,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FK</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -789,8 +762,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -563,15 +593,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -590,15 +630,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -617,15 +667,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
@@ -644,15 +700,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
@@ -671,15 +733,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
@@ -698,15 +766,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
@@ -725,43 +799,49 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -508,7 +514,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott och hälsa 1 med didaktisk inriktning'</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -541,7 +548,12 @@
           <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -574,7 +586,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -611,7 +624,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -648,7 +666,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -681,7 +704,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
@@ -714,7 +742,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
@@ -747,7 +780,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
@@ -780,7 +818,12 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
@@ -813,35 +856,40 @@
           <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:H11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Idrott`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Organisation` → `FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -562,41 +562,49 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Idrott 2'</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>`Organisation`</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -606,12 +614,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-01-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -631,14 +639,14 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -648,14 +656,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2019-10-29</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2023-01-19</t>
-        </is>
-      </c>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -673,14 +677,14 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,14 +715,14 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -728,7 +732,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -749,14 +753,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -787,14 +791,14 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -804,7 +808,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -825,50 +829,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>GSA3FK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SAA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>`Organisation`</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>`FEB021` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -888,8 +854,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
